--- a/КТП/КТП 26-27/Распределение часов по КТП 2026-2027.xlsx
+++ b/КТП/КТП 26-27/Распределение часов по КТП 2026-2027.xlsx
@@ -10189,7 +10189,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="305" hidden="1" spans="1:5">
+    <row r="305" spans="1:5">
       <c r="A305" s="1">
         <v>46266</v>
       </c>
@@ -10203,7 +10203,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="306" hidden="1" spans="1:5">
+    <row r="306" spans="1:5">
       <c r="A306" s="1">
         <v>46267</v>
       </c>
@@ -10217,7 +10217,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="307" hidden="1" spans="1:5">
+    <row r="307" spans="1:5">
       <c r="A307" s="1">
         <v>46268</v>
       </c>
@@ -10231,7 +10231,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="308" hidden="1" spans="1:5">
+    <row r="308" spans="1:5">
       <c r="A308" s="1">
         <v>46269</v>
       </c>
@@ -10245,7 +10245,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="309" hidden="1" spans="1:5">
+    <row r="309" spans="1:5">
       <c r="A309" s="1">
         <v>46270</v>
       </c>
@@ -10259,7 +10259,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="310" hidden="1" spans="1:5">
+    <row r="310" spans="1:5">
       <c r="A310" s="1">
         <v>46271</v>
       </c>
@@ -10273,7 +10273,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="311" hidden="1" spans="1:5">
+    <row r="311" spans="1:5">
       <c r="A311" s="1">
         <v>46272</v>
       </c>
@@ -10290,7 +10290,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="312" hidden="1" spans="1:5">
+    <row r="312" spans="1:5">
       <c r="A312" s="1">
         <v>46273</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" hidden="1" spans="1:5">
+    <row r="313" spans="1:5">
       <c r="A313" s="1">
         <v>46274</v>
       </c>
@@ -10321,7 +10321,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="314" hidden="1" spans="1:5">
+    <row r="314" spans="1:5">
       <c r="A314" s="1">
         <v>46275</v>
       </c>
@@ -10335,7 +10335,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="315" hidden="1" spans="1:5">
+    <row r="315" spans="1:5">
       <c r="A315" s="1">
         <v>46276</v>
       </c>
@@ -10349,7 +10349,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="316" hidden="1" spans="1:5">
+    <row r="316" spans="1:5">
       <c r="A316" s="1">
         <v>46277</v>
       </c>
@@ -10363,7 +10363,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="317" hidden="1" spans="1:5">
+    <row r="317" spans="1:5">
       <c r="A317" s="1">
         <v>46278</v>
       </c>
@@ -10377,7 +10377,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="318" hidden="1" spans="1:5">
+    <row r="318" spans="1:5">
       <c r="A318" s="1">
         <v>46279</v>
       </c>
@@ -10394,7 +10394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319" hidden="1" spans="1:5">
+    <row r="319" spans="1:5">
       <c r="A319" s="1">
         <v>46280</v>
       </c>
@@ -10408,7 +10408,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="320" hidden="1" spans="1:5">
+    <row r="320" spans="1:5">
       <c r="A320" s="1">
         <v>46281</v>
       </c>
@@ -10422,7 +10422,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="321" hidden="1" spans="1:7">
+    <row r="321" spans="1:7">
       <c r="A321" s="1">
         <v>46282</v>
       </c>
@@ -10436,7 +10436,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="322" hidden="1" spans="1:7">
+    <row r="322" spans="1:7">
       <c r="A322" s="1">
         <v>46283</v>
       </c>
@@ -10450,7 +10450,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="323" hidden="1" spans="1:7">
+    <row r="323" spans="1:7">
       <c r="A323" s="1">
         <v>46284</v>
       </c>
@@ -10464,7 +10464,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="324" hidden="1" spans="1:7">
+    <row r="324" spans="1:7">
       <c r="A324" s="1">
         <v>46285</v>
       </c>
@@ -10481,7 +10481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="325" hidden="1" spans="1:7">
+    <row r="325" spans="1:7">
       <c r="A325" s="1">
         <v>46286</v>
       </c>
@@ -10498,7 +10498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="326" hidden="1" spans="1:7">
+    <row r="326" spans="1:7">
       <c r="A326" s="1">
         <v>46287</v>
       </c>
@@ -10512,7 +10512,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="327" hidden="1" spans="1:7">
+    <row r="327" spans="1:7">
       <c r="A327" s="1">
         <v>46288</v>
       </c>
@@ -10526,7 +10526,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="328" hidden="1" spans="1:7">
+    <row r="328" spans="1:7">
       <c r="A328" s="1">
         <v>46289</v>
       </c>
@@ -10540,7 +10540,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="329" hidden="1" spans="1:7">
+    <row r="329" spans="1:7">
       <c r="A329" s="1">
         <v>46290</v>
       </c>
@@ -10554,7 +10554,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="330" hidden="1" spans="1:7">
+    <row r="330" spans="1:7">
       <c r="A330" s="1">
         <v>46291</v>
       </c>
@@ -10568,7 +10568,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="331" hidden="1" spans="1:7">
+    <row r="331" spans="1:7">
       <c r="A331" s="1">
         <v>46292</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="332" hidden="1" spans="1:7">
+    <row r="332" spans="1:7">
       <c r="A332" s="1">
         <v>46293</v>
       </c>
@@ -10599,7 +10599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="333" hidden="1" spans="1:7">
+    <row r="333" spans="1:7">
       <c r="A333" s="1">
         <v>46294</v>
       </c>
@@ -10613,7 +10613,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="334" hidden="1" spans="1:7">
+    <row r="334" spans="1:7">
       <c r="A334" s="1">
         <v>46295</v>
       </c>
@@ -41302,7 +41302,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2426" spans="1:5">
+    <row r="2426" hidden="1" spans="1:5">
       <c r="A2426" s="1">
         <v>46266</v>
       </c>
@@ -41316,7 +41316,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2427" spans="1:5">
+    <row r="2427" hidden="1" spans="1:5">
       <c r="A2427" s="1">
         <v>46267</v>
       </c>
@@ -41330,7 +41330,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2428" spans="1:5">
+    <row r="2428" hidden="1" spans="1:5">
       <c r="A2428" s="1">
         <v>46268</v>
       </c>
@@ -41347,7 +41347,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2429" spans="1:5">
+    <row r="2429" hidden="1" spans="1:5">
       <c r="A2429" s="1">
         <v>46269</v>
       </c>
@@ -41361,7 +41361,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2430" spans="1:5">
+    <row r="2430" hidden="1" spans="1:5">
       <c r="A2430" s="1">
         <v>46270</v>
       </c>
@@ -41378,7 +41378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2431" spans="1:5">
+    <row r="2431" hidden="1" spans="1:5">
       <c r="A2431" s="1">
         <v>46271</v>
       </c>
@@ -41392,7 +41392,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2432" spans="1:5">
+    <row r="2432" hidden="1" spans="1:5">
       <c r="A2432" s="1">
         <v>46272</v>
       </c>
@@ -41406,7 +41406,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2433" spans="1:5">
+    <row r="2433" hidden="1" spans="1:5">
       <c r="A2433" s="1">
         <v>46273</v>
       </c>
@@ -41420,7 +41420,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2434" spans="1:5">
+    <row r="2434" hidden="1" spans="1:5">
       <c r="A2434" s="1">
         <v>46274</v>
       </c>
@@ -41434,7 +41434,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2435" spans="1:5">
+    <row r="2435" hidden="1" spans="1:5">
       <c r="A2435" s="1">
         <v>46275</v>
       </c>
@@ -41451,7 +41451,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2436" spans="1:5">
+    <row r="2436" hidden="1" spans="1:5">
       <c r="A2436" s="1">
         <v>46276</v>
       </c>
@@ -41465,7 +41465,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2437" spans="1:5">
+    <row r="2437" hidden="1" spans="1:5">
       <c r="A2437" s="1">
         <v>46277</v>
       </c>
@@ -41482,7 +41482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2438" spans="1:5">
+    <row r="2438" hidden="1" spans="1:5">
       <c r="A2438" s="1">
         <v>46278</v>
       </c>
@@ -41499,7 +41499,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2439" spans="1:5">
+    <row r="2439" hidden="1" spans="1:5">
       <c r="A2439" s="1">
         <v>46279</v>
       </c>
@@ -41513,7 +41513,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2440" spans="1:5">
+    <row r="2440" hidden="1" spans="1:5">
       <c r="A2440" s="1">
         <v>46280</v>
       </c>
@@ -41527,7 +41527,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2441" spans="1:5">
+    <row r="2441" hidden="1" spans="1:5">
       <c r="A2441" s="1">
         <v>46281</v>
       </c>
@@ -41541,7 +41541,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2442" spans="1:5">
+    <row r="2442" hidden="1" spans="1:5">
       <c r="A2442" s="1">
         <v>46282</v>
       </c>
@@ -41558,7 +41558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2443" spans="1:5">
+    <row r="2443" hidden="1" spans="1:5">
       <c r="A2443" s="1">
         <v>46283</v>
       </c>
@@ -41572,7 +41572,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2444" spans="1:5">
+    <row r="2444" hidden="1" spans="1:5">
       <c r="A2444" s="1">
         <v>46284</v>
       </c>
@@ -41589,7 +41589,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2445" spans="1:5">
+    <row r="2445" hidden="1" spans="1:5">
       <c r="A2445" s="1">
         <v>46285</v>
       </c>
@@ -41603,7 +41603,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2446" spans="1:5">
+    <row r="2446" hidden="1" spans="1:5">
       <c r="A2446" s="1">
         <v>46286</v>
       </c>
@@ -41617,7 +41617,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2447" spans="1:5">
+    <row r="2447" hidden="1" spans="1:5">
       <c r="A2447" s="1">
         <v>46287</v>
       </c>
@@ -41631,7 +41631,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2448" spans="1:5">
+    <row r="2448" hidden="1" spans="1:5">
       <c r="A2448" s="1">
         <v>46288</v>
       </c>
@@ -41645,7 +41645,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2449" spans="1:7">
+    <row r="2449" hidden="1" spans="1:7">
       <c r="A2449" s="1">
         <v>46289</v>
       </c>
@@ -41662,7 +41662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2450" spans="1:7">
+    <row r="2450" hidden="1" spans="1:7">
       <c r="A2450" s="1">
         <v>46290</v>
       </c>
@@ -41676,7 +41676,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2451" spans="1:7">
+    <row r="2451" hidden="1" spans="1:7">
       <c r="A2451" s="1">
         <v>46291</v>
       </c>
@@ -41693,7 +41693,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2452" spans="1:7">
+    <row r="2452" hidden="1" spans="1:7">
       <c r="A2452" s="1">
         <v>46292</v>
       </c>
@@ -41707,7 +41707,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2453" spans="1:7">
+    <row r="2453" hidden="1" spans="1:7">
       <c r="A2453" s="1">
         <v>46293</v>
       </c>
@@ -41721,7 +41721,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2454" spans="1:7">
+    <row r="2454" hidden="1" spans="1:7">
       <c r="A2454" s="1">
         <v>46294</v>
       </c>
@@ -41735,7 +41735,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2455" spans="1:7">
+    <row r="2455" hidden="1" spans="1:7">
       <c r="A2455" s="1">
         <v>46295</v>
       </c>
@@ -50235,7 +50235,7 @@
     </filterColumn>
     <filterColumn colId="2">
       <filters>
-        <filter val="401"/>
+        <filter val="21"/>
       </filters>
     </filterColumn>
     <filterColumn colId="3">
